--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120272645</v>
+        <v>120272566</v>
       </c>
       <c r="B2" t="n">
-        <v>56514</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624550</v>
+        <v>624519</v>
       </c>
       <c r="R2" t="n">
-        <v>7022411</v>
+        <v>7022450</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120272566</v>
+        <v>120272645</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>56514</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624519</v>
+        <v>624550</v>
       </c>
       <c r="R3" t="n">
-        <v>7022450</v>
+        <v>7022411</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -1514,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120273602</v>
+        <v>120272371</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,38 +1526,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624807</v>
+        <v>624367</v>
       </c>
       <c r="R10" t="n">
-        <v>7022242</v>
+        <v>7022541</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120272371</v>
+        <v>120273602</v>
       </c>
       <c r="B11" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,38 +1628,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624367</v>
+        <v>624807</v>
       </c>
       <c r="R11" t="n">
-        <v>7022541</v>
+        <v>7022242</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120273620</v>
+        <v>120273696</v>
       </c>
       <c r="B19" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624821</v>
+        <v>624864</v>
       </c>
       <c r="R19" t="n">
-        <v>7022234</v>
+        <v>7022217</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273696</v>
+        <v>120273620</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624864</v>
+        <v>624821</v>
       </c>
       <c r="R20" t="n">
-        <v>7022217</v>
+        <v>7022234</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120272229</v>
+        <v>120272628</v>
       </c>
       <c r="B23" t="n">
-        <v>90954</v>
+        <v>95202</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2865,20 +2865,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>2869</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2888,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624381</v>
+        <v>624550</v>
       </c>
       <c r="R23" t="n">
-        <v>7022482</v>
+        <v>7022411</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2950,10 +2955,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120272628</v>
+        <v>120273627</v>
       </c>
       <c r="B24" t="n">
-        <v>95202</v>
+        <v>90562</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2962,38 +2967,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624550</v>
+        <v>624821</v>
       </c>
       <c r="R24" t="n">
-        <v>7022411</v>
+        <v>7022235</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3052,10 +3057,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120273627</v>
+        <v>120273257</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3068,34 +3073,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624821</v>
+        <v>624814</v>
       </c>
       <c r="R25" t="n">
-        <v>7022235</v>
+        <v>7022378</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,6 +3138,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3154,10 +3169,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120273257</v>
+        <v>120272229</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>90954</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3170,39 +3185,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624814</v>
+        <v>624381</v>
       </c>
       <c r="R26" t="n">
-        <v>7022378</v>
+        <v>7022482</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3235,11 +3240,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120272566</v>
+        <v>120272645</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>56514</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624519</v>
+        <v>624550</v>
       </c>
       <c r="R2" t="n">
-        <v>7022450</v>
+        <v>7022411</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120272645</v>
+        <v>120272566</v>
       </c>
       <c r="B3" t="n">
-        <v>56514</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624550</v>
+        <v>624519</v>
       </c>
       <c r="R3" t="n">
-        <v>7022411</v>
+        <v>7022450</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -2445,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120273696</v>
+        <v>120273620</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624864</v>
+        <v>624821</v>
       </c>
       <c r="R19" t="n">
-        <v>7022217</v>
+        <v>7022234</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273620</v>
+        <v>120273696</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624821</v>
+        <v>624864</v>
       </c>
       <c r="R20" t="n">
-        <v>7022234</v>
+        <v>7022217</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120272645</v>
+        <v>120272229</v>
       </c>
       <c r="B2" t="n">
-        <v>56514</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624550</v>
+        <v>624381</v>
       </c>
       <c r="R2" t="n">
-        <v>7022411</v>
+        <v>7022482</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120272566</v>
+        <v>120272432</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +784,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624519</v>
+        <v>624396</v>
       </c>
       <c r="R3" t="n">
-        <v>7022450</v>
+        <v>7022500</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120272200</v>
+        <v>120272485</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,43 +886,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624385</v>
+        <v>624449</v>
       </c>
       <c r="R4" t="n">
-        <v>7022487</v>
+        <v>7022507</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120273078</v>
+        <v>120272677</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,42 +988,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624816</v>
+        <v>624576</v>
       </c>
       <c r="R5" t="n">
-        <v>7022282</v>
+        <v>7022395</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1102,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120273496</v>
+        <v>120271439</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,45 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624803</v>
+        <v>624523</v>
       </c>
       <c r="R6" t="n">
-        <v>7022244</v>
+        <v>7022199</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120272073</v>
+        <v>120272628</v>
       </c>
       <c r="B7" t="n">
-        <v>90582</v>
+        <v>95225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624349</v>
+        <v>624550</v>
       </c>
       <c r="R7" t="n">
-        <v>7022391</v>
+        <v>7022411</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120272432</v>
+        <v>120272566</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>90545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624396</v>
+        <v>624519</v>
       </c>
       <c r="R8" t="n">
-        <v>7022500</v>
+        <v>7022450</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1412,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120272004</v>
+        <v>120273575</v>
       </c>
       <c r="B9" t="n">
-        <v>91863</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,37 +1405,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624404</v>
+        <v>624807</v>
       </c>
       <c r="R9" t="n">
-        <v>7022301</v>
+        <v>7022241</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120272371</v>
+        <v>120273696</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624367</v>
+        <v>624864</v>
       </c>
       <c r="R10" t="n">
-        <v>7022541</v>
+        <v>7022217</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1616,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120273602</v>
+        <v>120272558</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,14 +1629,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624807</v>
+        <v>624517</v>
       </c>
       <c r="R11" t="n">
-        <v>7022242</v>
+        <v>7022444</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1718,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120272677</v>
+        <v>120272420</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,31 +1707,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1763,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624576</v>
+        <v>624396</v>
       </c>
       <c r="R12" t="n">
-        <v>7022395</v>
+        <v>7022500</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1825,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120272485</v>
+        <v>120273570</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,38 +1813,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624449</v>
+        <v>624807</v>
       </c>
       <c r="R13" t="n">
-        <v>7022507</v>
+        <v>7022241</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1927,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120272420</v>
+        <v>120273620</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,42 +1919,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624396</v>
+        <v>624821</v>
       </c>
       <c r="R14" t="n">
-        <v>7022500</v>
+        <v>7022234</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2033,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120271697</v>
+        <v>120273790</v>
       </c>
       <c r="B15" t="n">
-        <v>78262</v>
+        <v>90527</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2049,37 +2025,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624458</v>
+        <v>624930</v>
       </c>
       <c r="R15" t="n">
-        <v>7022273</v>
+        <v>7022199</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2135,10 +2111,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120273790</v>
+        <v>120273627</v>
       </c>
       <c r="B16" t="n">
-        <v>90509</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2127,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624930</v>
+        <v>624821</v>
       </c>
       <c r="R16" t="n">
-        <v>7022199</v>
+        <v>7022235</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2237,10 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120272558</v>
+        <v>120273257</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,34 +2229,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624517</v>
+        <v>624814</v>
       </c>
       <c r="R17" t="n">
-        <v>7022444</v>
+        <v>7022378</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2313,6 +2294,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120273570</v>
+        <v>120273496</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,7 +2360,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2383,10 +2369,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624807</v>
+        <v>624803</v>
       </c>
       <c r="R18" t="n">
-        <v>7022241</v>
+        <v>7022244</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2445,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120273620</v>
+        <v>120272073</v>
       </c>
       <c r="B19" t="n">
-        <v>90846</v>
+        <v>90600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,37 +2447,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624821</v>
+        <v>624349</v>
       </c>
       <c r="R19" t="n">
-        <v>7022234</v>
+        <v>7022391</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2547,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273696</v>
+        <v>120272371</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2559,38 +2545,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624864</v>
+        <v>624367</v>
       </c>
       <c r="R20" t="n">
-        <v>7022217</v>
+        <v>7022541</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2649,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120271439</v>
+        <v>120272200</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,37 +2651,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624523</v>
+        <v>624385</v>
       </c>
       <c r="R21" t="n">
-        <v>7022199</v>
+        <v>7022487</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2725,6 +2716,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2751,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120273575</v>
+        <v>120272645</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
+        <v>56524</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,34 +2763,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624807</v>
+        <v>624550</v>
       </c>
       <c r="R22" t="n">
-        <v>7022241</v>
+        <v>7022411</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2853,10 +2854,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120272628</v>
+        <v>120272004</v>
       </c>
       <c r="B23" t="n">
-        <v>95202</v>
+        <v>91881</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2865,25 +2866,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2893,13 +2894,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624550</v>
+        <v>624404</v>
       </c>
       <c r="R23" t="n">
-        <v>7022411</v>
+        <v>7022301</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2955,10 +2956,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120273627</v>
+        <v>120273602</v>
       </c>
       <c r="B24" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,10 +2996,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624821</v>
+        <v>624807</v>
       </c>
       <c r="R24" t="n">
-        <v>7022235</v>
+        <v>7022242</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3057,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120273257</v>
+        <v>120273078</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3069,31 +3070,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624814</v>
+        <v>624816</v>
       </c>
       <c r="R25" t="n">
-        <v>7022378</v>
+        <v>7022282</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3138,11 +3138,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3169,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120272229</v>
+        <v>120271697</v>
       </c>
       <c r="B26" t="n">
-        <v>90954</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3185,16 +3180,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3204,13 +3204,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624381</v>
+        <v>624458</v>
       </c>
       <c r="R26" t="n">
-        <v>7022482</v>
+        <v>7022273</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120272677</v>
+        <v>120271439</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -992,42 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624576</v>
+        <v>624523</v>
       </c>
       <c r="R5" t="n">
-        <v>7022395</v>
+        <v>7022199</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120271439</v>
+        <v>120272628</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1090,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1118,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624523</v>
+        <v>624550</v>
       </c>
       <c r="R6" t="n">
-        <v>7022199</v>
+        <v>7022411</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120272628</v>
+        <v>120272677</v>
       </c>
       <c r="B7" t="n">
-        <v>95225</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1192,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624550</v>
+        <v>624576</v>
       </c>
       <c r="R7" t="n">
-        <v>7022411</v>
+        <v>7022395</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120273602</v>
+        <v>120273078</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,38 +2968,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624807</v>
+        <v>624816</v>
       </c>
       <c r="R24" t="n">
-        <v>7022242</v>
+        <v>7022282</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3058,10 +3062,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120273078</v>
+        <v>120273602</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3070,42 +3074,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624816</v>
+        <v>624807</v>
       </c>
       <c r="R25" t="n">
-        <v>7022282</v>
+        <v>7022242</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120272229</v>
+        <v>120273575</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040186</v>
+        <v>658</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624381</v>
+        <v>624807</v>
       </c>
       <c r="R2" t="n">
-        <v>7022482</v>
+        <v>7022241</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120272432</v>
+        <v>120273627</v>
       </c>
       <c r="B3" t="n">
         <v>90580</v>
@@ -808,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624396</v>
+        <v>624821</v>
       </c>
       <c r="R3" t="n">
-        <v>7022500</v>
+        <v>7022235</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120272485</v>
+        <v>120272371</v>
       </c>
       <c r="B4" t="n">
         <v>90545</v>
@@ -914,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624449</v>
+        <v>624367</v>
       </c>
       <c r="R4" t="n">
-        <v>7022507</v>
+        <v>7022541</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120271439</v>
+        <v>120272432</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -992,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624523</v>
+        <v>624396</v>
       </c>
       <c r="R5" t="n">
-        <v>7022199</v>
+        <v>7022500</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120272628</v>
+        <v>120271439</v>
       </c>
       <c r="B6" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1090,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624550</v>
+        <v>624523</v>
       </c>
       <c r="R6" t="n">
-        <v>7022411</v>
+        <v>7022199</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120272566</v>
+        <v>120272229</v>
       </c>
       <c r="B8" t="n">
-        <v>90545</v>
+        <v>90972</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624519</v>
+        <v>624381</v>
       </c>
       <c r="R8" t="n">
-        <v>7022450</v>
+        <v>7022482</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120273575</v>
+        <v>120272645</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>56524</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624807</v>
+        <v>624550</v>
       </c>
       <c r="R9" t="n">
-        <v>7022241</v>
+        <v>7022411</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120273696</v>
+        <v>120273078</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1508,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624864</v>
+        <v>624816</v>
       </c>
       <c r="R10" t="n">
-        <v>7022217</v>
+        <v>7022282</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1695,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120272420</v>
+        <v>120273496</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1730,19 +1739,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624396</v>
+        <v>624803</v>
       </c>
       <c r="R12" t="n">
-        <v>7022500</v>
+        <v>7022244</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1801,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120273570</v>
+        <v>120272420</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1836,19 +1845,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624807</v>
+        <v>624396</v>
       </c>
       <c r="R13" t="n">
-        <v>7022241</v>
+        <v>7022500</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1907,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120273620</v>
+        <v>120272566</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,38 +1928,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624821</v>
+        <v>624519</v>
       </c>
       <c r="R14" t="n">
-        <v>7022234</v>
+        <v>7022450</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2009,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120273790</v>
+        <v>120272200</v>
       </c>
       <c r="B15" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2025,34 +2034,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624930</v>
+        <v>624385</v>
       </c>
       <c r="R15" t="n">
-        <v>7022199</v>
+        <v>7022487</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2085,6 +2099,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120273627</v>
+        <v>120273790</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2127,21 +2146,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2151,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624821</v>
+        <v>624930</v>
       </c>
       <c r="R16" t="n">
-        <v>7022235</v>
+        <v>7022199</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2213,10 +2232,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120273257</v>
+        <v>120273696</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2229,39 +2248,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624814</v>
+        <v>624864</v>
       </c>
       <c r="R17" t="n">
-        <v>7022378</v>
+        <v>7022217</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2294,11 +2308,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,10 +2334,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120273496</v>
+        <v>120273620</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,42 +2346,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624803</v>
+        <v>624821</v>
       </c>
       <c r="R18" t="n">
-        <v>7022244</v>
+        <v>7022234</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2431,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120272073</v>
+        <v>120273570</v>
       </c>
       <c r="B19" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,41 +2448,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624349</v>
+        <v>624807</v>
       </c>
       <c r="R19" t="n">
-        <v>7022391</v>
+        <v>7022241</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2533,10 +2542,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120272371</v>
+        <v>120272073</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>90600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,41 +2554,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624367</v>
+        <v>624349</v>
       </c>
       <c r="R20" t="n">
-        <v>7022541</v>
+        <v>7022391</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2635,10 +2644,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120272200</v>
+        <v>120273602</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,39 +2660,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624385</v>
+        <v>624807</v>
       </c>
       <c r="R21" t="n">
-        <v>7022487</v>
+        <v>7022242</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2716,11 +2720,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2747,10 +2746,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120272645</v>
+        <v>120273257</v>
       </c>
       <c r="B22" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2763,16 +2762,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2783,19 +2782,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624550</v>
+        <v>624814</v>
       </c>
       <c r="R22" t="n">
-        <v>7022411</v>
+        <v>7022378</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2828,6 +2827,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2854,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120272004</v>
+        <v>120272628</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>95225</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2866,25 +2870,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>2869</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2894,13 +2898,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624404</v>
+        <v>624550</v>
       </c>
       <c r="R23" t="n">
-        <v>7022301</v>
+        <v>7022411</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2956,10 +2960,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120273078</v>
+        <v>120272004</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,45 +2972,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624816</v>
+        <v>624404</v>
       </c>
       <c r="R24" t="n">
-        <v>7022282</v>
+        <v>7022301</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120273602</v>
+        <v>120271697</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>78278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3078,37 +3078,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624807</v>
+        <v>624458</v>
       </c>
       <c r="R25" t="n">
-        <v>7022242</v>
+        <v>7022273</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120271697</v>
+        <v>120272485</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,41 +3176,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624458</v>
+        <v>624449</v>
       </c>
       <c r="R26" t="n">
-        <v>7022273</v>
+        <v>7022507</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -2018,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120272200</v>
+        <v>120273696</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2034,39 +2034,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624385</v>
+        <v>624864</v>
       </c>
       <c r="R15" t="n">
-        <v>7022487</v>
+        <v>7022217</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2099,11 +2094,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2130,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120273790</v>
+        <v>120272200</v>
       </c>
       <c r="B16" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2146,34 +2136,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624930</v>
+        <v>624385</v>
       </c>
       <c r="R16" t="n">
-        <v>7022199</v>
+        <v>7022487</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2206,6 +2201,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120273696</v>
+        <v>120273790</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2248,21 +2248,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624864</v>
+        <v>624930</v>
       </c>
       <c r="R17" t="n">
-        <v>7022217</v>
+        <v>7022199</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120273575</v>
+        <v>120271439</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624807</v>
+        <v>624523</v>
       </c>
       <c r="R2" t="n">
-        <v>7022241</v>
+        <v>7022199</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120273627</v>
+        <v>120273696</v>
       </c>
       <c r="B3" t="n">
         <v>90580</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624821</v>
+        <v>624864</v>
       </c>
       <c r="R3" t="n">
-        <v>7022235</v>
+        <v>7022217</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120272371</v>
+        <v>120272677</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624367</v>
+        <v>624576</v>
       </c>
       <c r="R4" t="n">
-        <v>7022541</v>
+        <v>7022395</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120272432</v>
+        <v>120272628</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>95225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624396</v>
+        <v>624550</v>
       </c>
       <c r="R5" t="n">
-        <v>7022500</v>
+        <v>7022411</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120271439</v>
+        <v>120272485</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1100,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624523</v>
+        <v>624449</v>
       </c>
       <c r="R6" t="n">
-        <v>7022199</v>
+        <v>7022507</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120272677</v>
+        <v>120273575</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,39 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624576</v>
+        <v>624807</v>
       </c>
       <c r="R7" t="n">
-        <v>7022395</v>
+        <v>7022241</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120272229</v>
+        <v>120272004</v>
       </c>
       <c r="B8" t="n">
-        <v>90972</v>
+        <v>91881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,16 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624381</v>
+        <v>624404</v>
       </c>
       <c r="R8" t="n">
-        <v>7022482</v>
+        <v>7022301</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120272645</v>
+        <v>120273570</v>
       </c>
       <c r="B9" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,43 +1406,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624550</v>
+        <v>624807</v>
       </c>
       <c r="R9" t="n">
-        <v>7022411</v>
+        <v>7022241</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1602,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120272558</v>
+        <v>120272073</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>90600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1622,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,13 +1646,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624517</v>
+        <v>624349</v>
       </c>
       <c r="R11" t="n">
-        <v>7022444</v>
+        <v>7022391</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120273496</v>
+        <v>120273790</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,42 +1720,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624803</v>
+        <v>624930</v>
       </c>
       <c r="R12" t="n">
-        <v>7022244</v>
+        <v>7022199</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120272420</v>
+        <v>120273620</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,42 +1822,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624396</v>
+        <v>624821</v>
       </c>
       <c r="R13" t="n">
-        <v>7022500</v>
+        <v>7022234</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1916,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120272566</v>
+        <v>120272645</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>56524</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,38 +1924,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624519</v>
+        <v>624550</v>
       </c>
       <c r="R14" t="n">
-        <v>7022450</v>
+        <v>7022411</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,7 +2019,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120273696</v>
+        <v>120272558</v>
       </c>
       <c r="B15" t="n">
         <v>90580</v>
@@ -2054,14 +2055,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624864</v>
+        <v>624517</v>
       </c>
       <c r="R15" t="n">
-        <v>7022217</v>
+        <v>7022444</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2120,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120272200</v>
+        <v>120272432</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,39 +2137,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624385</v>
+        <v>624396</v>
       </c>
       <c r="R16" t="n">
-        <v>7022487</v>
+        <v>7022500</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2201,11 +2197,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120273790</v>
+        <v>120273627</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2248,21 +2239,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2272,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624930</v>
+        <v>624821</v>
       </c>
       <c r="R17" t="n">
-        <v>7022199</v>
+        <v>7022235</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2334,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120273620</v>
+        <v>120272566</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,38 +2337,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624821</v>
+        <v>624519</v>
       </c>
       <c r="R18" t="n">
-        <v>7022234</v>
+        <v>7022450</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2436,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120273570</v>
+        <v>120272371</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,42 +2439,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624807</v>
+        <v>624367</v>
       </c>
       <c r="R19" t="n">
-        <v>7022241</v>
+        <v>7022541</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2542,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120272073</v>
+        <v>120273257</v>
       </c>
       <c r="B20" t="n">
-        <v>90600</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2558,37 +2545,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624349</v>
+        <v>624814</v>
       </c>
       <c r="R20" t="n">
-        <v>7022391</v>
+        <v>7022378</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,6 +2610,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2644,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120273602</v>
+        <v>120272420</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2656,38 +2653,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624807</v>
+        <v>624396</v>
       </c>
       <c r="R21" t="n">
-        <v>7022242</v>
+        <v>7022500</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2746,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120273257</v>
+        <v>120273602</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2762,39 +2763,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624814</v>
+        <v>624807</v>
       </c>
       <c r="R22" t="n">
-        <v>7022378</v>
+        <v>7022242</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,11 +2823,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2858,10 +2849,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120272628</v>
+        <v>120271697</v>
       </c>
       <c r="B23" t="n">
-        <v>95225</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2870,25 +2861,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2898,13 +2889,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624550</v>
+        <v>624458</v>
       </c>
       <c r="R23" t="n">
-        <v>7022411</v>
+        <v>7022273</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2960,10 +2951,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120272004</v>
+        <v>120272229</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>90972</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2976,21 +2967,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3000,13 +2986,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624404</v>
+        <v>624381</v>
       </c>
       <c r="R24" t="n">
-        <v>7022301</v>
+        <v>7022482</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3062,10 +3048,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120271697</v>
+        <v>120272200</v>
       </c>
       <c r="B25" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3078,37 +3064,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624458</v>
+        <v>624385</v>
       </c>
       <c r="R25" t="n">
-        <v>7022273</v>
+        <v>7022487</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3138,6 +3129,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3164,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120272485</v>
+        <v>120273496</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,38 +3172,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624449</v>
+        <v>624803</v>
       </c>
       <c r="R26" t="n">
-        <v>7022507</v>
+        <v>7022244</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120273620</v>
+        <v>120272645</v>
       </c>
       <c r="B13" t="n">
-        <v>90864</v>
+        <v>56524</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,34 +1826,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624821</v>
+        <v>624550</v>
       </c>
       <c r="R13" t="n">
-        <v>7022234</v>
+        <v>7022411</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120272645</v>
+        <v>120273620</v>
       </c>
       <c r="B14" t="n">
-        <v>56524</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,39 +1933,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624550</v>
+        <v>624821</v>
       </c>
       <c r="R14" t="n">
-        <v>7022411</v>
+        <v>7022234</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120271439</v>
+        <v>120273627</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624523</v>
+        <v>624821</v>
       </c>
       <c r="R2" t="n">
-        <v>7022199</v>
+        <v>7022235</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120273696</v>
+        <v>120273078</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624864</v>
+        <v>624816</v>
       </c>
       <c r="R3" t="n">
-        <v>7022217</v>
+        <v>7022282</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120272677</v>
+        <v>120272628</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>95225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624576</v>
+        <v>624550</v>
       </c>
       <c r="R4" t="n">
-        <v>7022395</v>
+        <v>7022411</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120272628</v>
+        <v>120273620</v>
       </c>
       <c r="B5" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +997,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624550</v>
+        <v>624821</v>
       </c>
       <c r="R5" t="n">
-        <v>7022411</v>
+        <v>7022234</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120272485</v>
+        <v>120271439</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1099,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624449</v>
+        <v>624523</v>
       </c>
       <c r="R6" t="n">
-        <v>7022507</v>
+        <v>7022199</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120273575</v>
+        <v>120272229</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>90972</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1205,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624807</v>
+        <v>624381</v>
       </c>
       <c r="R7" t="n">
-        <v>7022241</v>
+        <v>7022482</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120272004</v>
+        <v>120272645</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>56524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,37 +1302,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624404</v>
+        <v>624550</v>
       </c>
       <c r="R8" t="n">
-        <v>7022301</v>
+        <v>7022411</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120273570</v>
+        <v>120273496</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1429,7 +1428,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1438,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624807</v>
+        <v>624803</v>
       </c>
       <c r="R9" t="n">
-        <v>7022241</v>
+        <v>7022244</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120273078</v>
+        <v>120272371</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,42 +1511,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624816</v>
+        <v>624367</v>
       </c>
       <c r="R10" t="n">
-        <v>7022282</v>
+        <v>7022541</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120272073</v>
+        <v>120272432</v>
       </c>
       <c r="B11" t="n">
-        <v>90600</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,21 +1617,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,13 +1641,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624349</v>
+        <v>624396</v>
       </c>
       <c r="R11" t="n">
-        <v>7022391</v>
+        <v>7022500</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120273790</v>
+        <v>120272073</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>90600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,37 +1719,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624930</v>
+        <v>624349</v>
       </c>
       <c r="R12" t="n">
-        <v>7022199</v>
+        <v>7022391</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1810,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120272645</v>
+        <v>120273602</v>
       </c>
       <c r="B13" t="n">
-        <v>56524</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,39 +1821,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624550</v>
+        <v>624807</v>
       </c>
       <c r="R13" t="n">
-        <v>7022411</v>
+        <v>7022242</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1917,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120273620</v>
+        <v>120273570</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,38 +1919,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624821</v>
+        <v>624807</v>
       </c>
       <c r="R14" t="n">
-        <v>7022234</v>
+        <v>7022241</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2019,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120272558</v>
+        <v>120271697</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,21 +2029,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,13 +2053,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624517</v>
+        <v>624458</v>
       </c>
       <c r="R15" t="n">
-        <v>7022444</v>
+        <v>7022273</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2121,7 +2115,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120272432</v>
+        <v>120273696</v>
       </c>
       <c r="B16" t="n">
         <v>90580</v>
@@ -2157,14 +2151,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624396</v>
+        <v>624864</v>
       </c>
       <c r="R16" t="n">
-        <v>7022500</v>
+        <v>7022217</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2223,10 +2217,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120273627</v>
+        <v>120272004</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>91881</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2239,37 +2233,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624821</v>
+        <v>624404</v>
       </c>
       <c r="R17" t="n">
-        <v>7022235</v>
+        <v>7022301</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2325,10 +2319,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120272566</v>
+        <v>120272677</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,38 +2331,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624519</v>
+        <v>624576</v>
       </c>
       <c r="R18" t="n">
-        <v>7022450</v>
+        <v>7022395</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2427,7 +2426,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120272371</v>
+        <v>120272566</v>
       </c>
       <c r="B19" t="n">
         <v>90545</v>
@@ -2463,14 +2462,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624367</v>
+        <v>624519</v>
       </c>
       <c r="R19" t="n">
-        <v>7022541</v>
+        <v>7022450</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2529,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273257</v>
+        <v>120273575</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,39 +2544,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624814</v>
+        <v>624807</v>
       </c>
       <c r="R20" t="n">
-        <v>7022378</v>
+        <v>7022241</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2610,11 +2604,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2641,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120272420</v>
+        <v>120273790</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,42 +2642,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624396</v>
+        <v>624930</v>
       </c>
       <c r="R21" t="n">
-        <v>7022500</v>
+        <v>7022199</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2747,10 +2732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120273602</v>
+        <v>120272200</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2763,34 +2748,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624807</v>
+        <v>624385</v>
       </c>
       <c r="R22" t="n">
-        <v>7022242</v>
+        <v>7022487</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2823,6 +2813,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2849,10 +2844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120271697</v>
+        <v>120273257</v>
       </c>
       <c r="B23" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2865,37 +2860,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624458</v>
+        <v>624814</v>
       </c>
       <c r="R23" t="n">
-        <v>7022273</v>
+        <v>7022378</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2925,6 +2925,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120272229</v>
+        <v>120272485</v>
       </c>
       <c r="B24" t="n">
-        <v>90972</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,33 +2968,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624381</v>
+        <v>624449</v>
       </c>
       <c r="R24" t="n">
-        <v>7022482</v>
+        <v>7022507</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3048,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120272200</v>
+        <v>120272420</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3060,31 +3070,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3093,10 +3102,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624385</v>
+        <v>624396</v>
       </c>
       <c r="R25" t="n">
-        <v>7022487</v>
+        <v>7022500</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3129,11 +3138,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3160,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120273496</v>
+        <v>120272558</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3172,42 +3176,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624803</v>
+        <v>624517</v>
       </c>
       <c r="R26" t="n">
-        <v>7022244</v>
+        <v>7022444</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120273627</v>
+        <v>120272628</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>95225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624821</v>
+        <v>624550</v>
       </c>
       <c r="R2" t="n">
-        <v>7022235</v>
+        <v>7022411</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120273078</v>
+        <v>120272566</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624816</v>
+        <v>624519</v>
       </c>
       <c r="R3" t="n">
-        <v>7022282</v>
+        <v>7022450</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120272628</v>
+        <v>120272485</v>
       </c>
       <c r="B4" t="n">
-        <v>95225</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624550</v>
+        <v>624449</v>
       </c>
       <c r="R4" t="n">
-        <v>7022411</v>
+        <v>7022507</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120273620</v>
+        <v>120273078</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624821</v>
+        <v>624816</v>
       </c>
       <c r="R5" t="n">
-        <v>7022234</v>
+        <v>7022282</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120271439</v>
+        <v>120272229</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1103,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,13 +1122,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624523</v>
+        <v>624381</v>
       </c>
       <c r="R6" t="n">
-        <v>7022199</v>
+        <v>7022482</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120272229</v>
+        <v>120273575</v>
       </c>
       <c r="B7" t="n">
-        <v>90972</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,29 +1200,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>658</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624381</v>
+        <v>624807</v>
       </c>
       <c r="R7" t="n">
-        <v>7022482</v>
+        <v>7022241</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1286,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120272645</v>
+        <v>120272420</v>
       </c>
       <c r="B8" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1298,31 +1298,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1331,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624550</v>
+        <v>624396</v>
       </c>
       <c r="R8" t="n">
-        <v>7022411</v>
+        <v>7022500</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120273496</v>
+        <v>120272558</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,42 +1404,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624803</v>
+        <v>624517</v>
       </c>
       <c r="R9" t="n">
-        <v>7022244</v>
+        <v>7022444</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120272371</v>
+        <v>120272073</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>90600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,41 +1506,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624367</v>
+        <v>624349</v>
       </c>
       <c r="R10" t="n">
-        <v>7022541</v>
+        <v>7022391</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120272432</v>
+        <v>120272200</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,34 +1612,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624396</v>
+        <v>624385</v>
       </c>
       <c r="R11" t="n">
-        <v>7022500</v>
+        <v>7022487</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,6 +1677,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120272073</v>
+        <v>120273496</v>
       </c>
       <c r="B12" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,41 +1720,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624349</v>
+        <v>624803</v>
       </c>
       <c r="R12" t="n">
-        <v>7022391</v>
+        <v>7022244</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,7 +1814,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120273602</v>
+        <v>120273696</v>
       </c>
       <c r="B13" t="n">
         <v>90580</v>
@@ -1845,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624807</v>
+        <v>624864</v>
       </c>
       <c r="R13" t="n">
-        <v>7022242</v>
+        <v>7022217</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1907,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120273570</v>
+        <v>120272677</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,42 +1928,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624807</v>
+        <v>624576</v>
       </c>
       <c r="R14" t="n">
-        <v>7022241</v>
+        <v>7022395</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2013,10 +2023,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120271697</v>
+        <v>120273570</v>
       </c>
       <c r="B15" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2025,41 +2035,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624458</v>
+        <v>624807</v>
       </c>
       <c r="R15" t="n">
-        <v>7022273</v>
+        <v>7022241</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2115,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120273696</v>
+        <v>120272004</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,37 +2145,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624864</v>
+        <v>624404</v>
       </c>
       <c r="R16" t="n">
-        <v>7022217</v>
+        <v>7022301</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2217,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120272004</v>
+        <v>120273620</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,37 +2247,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624404</v>
+        <v>624821</v>
       </c>
       <c r="R17" t="n">
-        <v>7022301</v>
+        <v>7022234</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2319,10 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120272677</v>
+        <v>120273790</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,39 +2349,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624576</v>
+        <v>624930</v>
       </c>
       <c r="R18" t="n">
-        <v>7022395</v>
+        <v>7022199</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2426,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120272566</v>
+        <v>120273257</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2438,38 +2447,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624519</v>
+        <v>624814</v>
       </c>
       <c r="R19" t="n">
-        <v>7022450</v>
+        <v>7022378</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2502,6 +2516,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273575</v>
+        <v>120272432</v>
       </c>
       <c r="B20" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2544,34 +2563,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624807</v>
+        <v>624396</v>
       </c>
       <c r="R20" t="n">
-        <v>7022241</v>
+        <v>7022500</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2630,10 +2649,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120273790</v>
+        <v>120271439</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2646,37 +2665,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624930</v>
+        <v>624523</v>
       </c>
       <c r="R21" t="n">
         <v>7022199</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2732,10 +2751,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120272200</v>
+        <v>120272371</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2744,43 +2763,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624385</v>
+        <v>624367</v>
       </c>
       <c r="R22" t="n">
-        <v>7022487</v>
+        <v>7022541</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2813,11 +2827,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2844,10 +2853,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120273257</v>
+        <v>120273627</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2860,39 +2869,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624814</v>
+        <v>624821</v>
       </c>
       <c r="R23" t="n">
-        <v>7022378</v>
+        <v>7022235</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2925,11 +2929,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,10 +2955,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120272485</v>
+        <v>120273602</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,38 +2967,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624449</v>
+        <v>624807</v>
       </c>
       <c r="R24" t="n">
-        <v>7022507</v>
+        <v>7022242</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3058,10 +3057,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120272420</v>
+        <v>120271697</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3070,45 +3069,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624396</v>
+        <v>624458</v>
       </c>
       <c r="R25" t="n">
-        <v>7022500</v>
+        <v>7022273</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3164,10 +3159,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120272558</v>
+        <v>120272645</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>56524</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3180,34 +3175,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624517</v>
+        <v>624550</v>
       </c>
       <c r="R26" t="n">
-        <v>7022444</v>
+        <v>7022411</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120272628</v>
+        <v>120273078</v>
       </c>
       <c r="B2" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624550</v>
+        <v>624816</v>
       </c>
       <c r="R2" t="n">
-        <v>7022411</v>
+        <v>7022282</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120272566</v>
+        <v>120272558</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624519</v>
+        <v>624517</v>
       </c>
       <c r="R3" t="n">
-        <v>7022450</v>
+        <v>7022444</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120272485</v>
+        <v>120273696</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624449</v>
+        <v>624864</v>
       </c>
       <c r="R4" t="n">
-        <v>7022507</v>
+        <v>7022217</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120273078</v>
+        <v>120272677</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,42 +997,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624816</v>
+        <v>624576</v>
       </c>
       <c r="R5" t="n">
-        <v>7022282</v>
+        <v>7022395</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1184,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120273575</v>
+        <v>120271439</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1200,37 +1205,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624807</v>
+        <v>624523</v>
       </c>
       <c r="R7" t="n">
-        <v>7022241</v>
+        <v>7022199</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1286,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120272420</v>
+        <v>120273790</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1298,42 +1303,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624396</v>
+        <v>624930</v>
       </c>
       <c r="R8" t="n">
-        <v>7022500</v>
+        <v>7022199</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120272558</v>
+        <v>120272004</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1408,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,13 +1433,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624517</v>
+        <v>624404</v>
       </c>
       <c r="R9" t="n">
-        <v>7022444</v>
+        <v>7022301</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120272073</v>
+        <v>120272371</v>
       </c>
       <c r="B10" t="n">
-        <v>90600</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1506,41 +1507,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624349</v>
+        <v>624367</v>
       </c>
       <c r="R10" t="n">
-        <v>7022391</v>
+        <v>7022541</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120272200</v>
+        <v>120271697</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1612,42 +1613,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624385</v>
+        <v>624458</v>
       </c>
       <c r="R11" t="n">
-        <v>7022487</v>
+        <v>7022273</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1677,11 +1673,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120273496</v>
+        <v>120272566</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,42 +1711,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624803</v>
+        <v>624519</v>
       </c>
       <c r="R12" t="n">
-        <v>7022244</v>
+        <v>7022450</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1814,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120273696</v>
+        <v>120272628</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>95225</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,38 +1813,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624864</v>
+        <v>624550</v>
       </c>
       <c r="R13" t="n">
-        <v>7022217</v>
+        <v>7022411</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1916,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120272677</v>
+        <v>120272200</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1932,16 +1919,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1961,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624576</v>
+        <v>624385</v>
       </c>
       <c r="R14" t="n">
-        <v>7022395</v>
+        <v>7022487</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1997,6 +1984,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2023,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120273570</v>
+        <v>120272073</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,45 +2027,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624807</v>
+        <v>624349</v>
       </c>
       <c r="R15" t="n">
-        <v>7022241</v>
+        <v>7022391</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2129,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120272004</v>
+        <v>120273570</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2141,41 +2129,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624404</v>
+        <v>624807</v>
       </c>
       <c r="R16" t="n">
-        <v>7022301</v>
+        <v>7022241</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120273620</v>
+        <v>120272432</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,34 +2239,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624821</v>
+        <v>624396</v>
       </c>
       <c r="R17" t="n">
-        <v>7022234</v>
+        <v>7022500</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2333,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120273790</v>
+        <v>120272645</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>56524</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,34 +2341,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624930</v>
+        <v>624550</v>
       </c>
       <c r="R18" t="n">
-        <v>7022199</v>
+        <v>7022411</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2435,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120273257</v>
+        <v>120273627</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,39 +2448,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624814</v>
+        <v>624821</v>
       </c>
       <c r="R19" t="n">
-        <v>7022378</v>
+        <v>7022235</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,11 +2508,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2547,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120272432</v>
+        <v>120273575</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,34 +2550,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624396</v>
+        <v>624807</v>
       </c>
       <c r="R20" t="n">
-        <v>7022500</v>
+        <v>7022241</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2649,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120271439</v>
+        <v>120273602</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,37 +2652,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624523</v>
+        <v>624807</v>
       </c>
       <c r="R21" t="n">
-        <v>7022199</v>
+        <v>7022242</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2751,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120272371</v>
+        <v>120272420</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2763,38 +2750,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624367</v>
+        <v>624396</v>
       </c>
       <c r="R22" t="n">
-        <v>7022541</v>
+        <v>7022500</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2853,10 +2844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120273627</v>
+        <v>120273496</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2865,38 +2856,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624821</v>
+        <v>624803</v>
       </c>
       <c r="R23" t="n">
-        <v>7022235</v>
+        <v>7022244</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2955,10 +2950,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120273602</v>
+        <v>120273620</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2971,21 +2966,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2995,10 +2990,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624807</v>
+        <v>624821</v>
       </c>
       <c r="R24" t="n">
-        <v>7022242</v>
+        <v>7022234</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3057,10 +3052,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120271697</v>
+        <v>120273257</v>
       </c>
       <c r="B25" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3073,37 +3068,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624458</v>
+        <v>624814</v>
       </c>
       <c r="R25" t="n">
-        <v>7022273</v>
+        <v>7022378</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3133,6 +3133,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3159,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120272645</v>
+        <v>120272485</v>
       </c>
       <c r="B26" t="n">
-        <v>56524</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3171,43 +3176,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624550</v>
+        <v>624449</v>
       </c>
       <c r="R26" t="n">
-        <v>7022411</v>
+        <v>7022507</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120272558</v>
+        <v>120272628</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>95225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624517</v>
+        <v>624550</v>
       </c>
       <c r="R3" t="n">
-        <v>7022444</v>
+        <v>7022411</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120273696</v>
+        <v>120273570</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +895,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624864</v>
+        <v>624807</v>
       </c>
       <c r="R4" t="n">
-        <v>7022217</v>
+        <v>7022241</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120272677</v>
+        <v>120272004</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,42 +1005,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624576</v>
+        <v>624404</v>
       </c>
       <c r="R5" t="n">
-        <v>7022395</v>
+        <v>7022301</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120272229</v>
+        <v>120273790</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>90527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,29 +1107,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>112</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624381</v>
+        <v>624930</v>
       </c>
       <c r="R6" t="n">
-        <v>7022482</v>
+        <v>7022199</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120271439</v>
+        <v>120273257</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,37 +1209,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624523</v>
+        <v>624814</v>
       </c>
       <c r="R7" t="n">
-        <v>7022199</v>
+        <v>7022378</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1265,6 +1274,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120273790</v>
+        <v>120273696</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624930</v>
+        <v>624864</v>
       </c>
       <c r="R8" t="n">
-        <v>7022199</v>
+        <v>7022217</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120272004</v>
+        <v>120271697</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>78278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624404</v>
+        <v>624458</v>
       </c>
       <c r="R9" t="n">
-        <v>7022301</v>
+        <v>7022273</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1495,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120272371</v>
+        <v>120273575</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,38 +1521,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624367</v>
+        <v>624807</v>
       </c>
       <c r="R10" t="n">
-        <v>7022541</v>
+        <v>7022241</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120271697</v>
+        <v>120272485</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,41 +1623,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624458</v>
+        <v>624449</v>
       </c>
       <c r="R11" t="n">
-        <v>7022273</v>
+        <v>7022507</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120272566</v>
+        <v>120272420</v>
       </c>
       <c r="B12" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,38 +1725,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624519</v>
+        <v>624396</v>
       </c>
       <c r="R12" t="n">
-        <v>7022450</v>
+        <v>7022500</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1801,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120272628</v>
+        <v>120273620</v>
       </c>
       <c r="B13" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,38 +1831,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624550</v>
+        <v>624821</v>
       </c>
       <c r="R13" t="n">
-        <v>7022411</v>
+        <v>7022234</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1903,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120272200</v>
+        <v>120273627</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,39 +1937,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624385</v>
+        <v>624821</v>
       </c>
       <c r="R14" t="n">
-        <v>7022487</v>
+        <v>7022235</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1984,11 +1997,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2015,10 +2023,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120272073</v>
+        <v>120272677</v>
       </c>
       <c r="B15" t="n">
-        <v>90600</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,37 +2039,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624349</v>
+        <v>624576</v>
       </c>
       <c r="R15" t="n">
-        <v>7022391</v>
+        <v>7022395</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2117,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120273570</v>
+        <v>120272432</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,42 +2142,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624807</v>
+        <v>624396</v>
       </c>
       <c r="R16" t="n">
-        <v>7022241</v>
+        <v>7022500</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2223,10 +2232,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120272432</v>
+        <v>120272073</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>90600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2239,21 +2248,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2263,13 +2272,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624396</v>
+        <v>624349</v>
       </c>
       <c r="R17" t="n">
-        <v>7022500</v>
+        <v>7022391</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2432,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120273627</v>
+        <v>120271439</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,37 +2457,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624821</v>
+        <v>624523</v>
       </c>
       <c r="R19" t="n">
-        <v>7022235</v>
+        <v>7022199</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2534,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273575</v>
+        <v>120273496</v>
       </c>
       <c r="B20" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,38 +2555,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624807</v>
+        <v>624803</v>
       </c>
       <c r="R20" t="n">
-        <v>7022241</v>
+        <v>7022244</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2636,10 +2649,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120273602</v>
+        <v>120272200</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,34 +2665,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624807</v>
+        <v>624385</v>
       </c>
       <c r="R21" t="n">
-        <v>7022242</v>
+        <v>7022487</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2712,6 +2730,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120272420</v>
+        <v>120272566</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2750,42 +2773,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624396</v>
+        <v>624519</v>
       </c>
       <c r="R22" t="n">
-        <v>7022500</v>
+        <v>7022450</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2844,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120273496</v>
+        <v>120272229</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>90972</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2856,42 +2875,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624803</v>
+        <v>624381</v>
       </c>
       <c r="R23" t="n">
-        <v>7022244</v>
+        <v>7022482</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2950,10 +2960,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120273620</v>
+        <v>120273602</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2966,21 +2976,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2990,10 +3000,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624821</v>
+        <v>624807</v>
       </c>
       <c r="R24" t="n">
-        <v>7022234</v>
+        <v>7022242</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3052,10 +3062,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120273257</v>
+        <v>120272558</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3068,39 +3078,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624814</v>
+        <v>624517</v>
       </c>
       <c r="R25" t="n">
-        <v>7022378</v>
+        <v>7022444</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,11 +3138,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3164,7 +3164,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120272485</v>
+        <v>120272371</v>
       </c>
       <c r="B26" t="n">
         <v>90545</v>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624449</v>
+        <v>624367</v>
       </c>
       <c r="R26" t="n">
-        <v>7022507</v>
+        <v>7022541</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120271697</v>
+        <v>120273575</v>
       </c>
       <c r="B9" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,37 +1423,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624458</v>
+        <v>624807</v>
       </c>
       <c r="R9" t="n">
-        <v>7022273</v>
+        <v>7022241</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120273575</v>
+        <v>120271697</v>
       </c>
       <c r="B10" t="n">
-        <v>90864</v>
+        <v>78278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,37 +1525,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624807</v>
+        <v>624458</v>
       </c>
       <c r="R10" t="n">
-        <v>7022241</v>
+        <v>7022273</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120272566</v>
+        <v>120272229</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>90972</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,25 +2773,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2801,10 +2796,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624519</v>
+        <v>624381</v>
       </c>
       <c r="R22" t="n">
-        <v>7022450</v>
+        <v>7022482</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2863,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120272229</v>
+        <v>120272566</v>
       </c>
       <c r="B23" t="n">
-        <v>90972</v>
+        <v>90545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,20 +2870,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624381</v>
+        <v>624519</v>
       </c>
       <c r="R23" t="n">
-        <v>7022482</v>
+        <v>7022450</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120273257</v>
+        <v>120273790</v>
       </c>
       <c r="B2" t="n">
-        <v>57332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624814</v>
+        <v>624930</v>
       </c>
       <c r="R2" t="n">
-        <v>7022378</v>
+        <v>7022199</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120272566</v>
+        <v>120273575</v>
       </c>
       <c r="B3" t="n">
-        <v>90595</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624519</v>
+        <v>624807</v>
       </c>
       <c r="R3" t="n">
-        <v>7022450</v>
+        <v>7022241</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120272371</v>
+        <v>120273620</v>
       </c>
       <c r="B4" t="n">
-        <v>90595</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624367</v>
+        <v>624821</v>
       </c>
       <c r="R4" t="n">
-        <v>7022541</v>
+        <v>7022234</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -994,12 +969,7 @@
         <v>120272432</v>
       </c>
       <c r="B5" t="n">
-        <v>90630</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120273790</v>
+        <v>120272558</v>
       </c>
       <c r="B6" t="n">
-        <v>90577</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624930</v>
+        <v>624517</v>
       </c>
       <c r="R6" t="n">
-        <v>7022199</v>
+        <v>7022444</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120272628</v>
+        <v>120273602</v>
       </c>
       <c r="B7" t="n">
-        <v>95294</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624550</v>
+        <v>624807</v>
       </c>
       <c r="R7" t="n">
-        <v>7022411</v>
+        <v>7022241</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,54 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120273570</v>
+        <v>120273627</v>
       </c>
       <c r="B8" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624807</v>
+        <v>624821</v>
       </c>
       <c r="R8" t="n">
-        <v>7022241</v>
+        <v>7022235</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120272229</v>
+        <v>120273696</v>
       </c>
       <c r="B9" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,29 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624381</v>
+        <v>624864</v>
       </c>
       <c r="R9" t="n">
-        <v>7022482</v>
+        <v>7022217</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120272073</v>
+        <v>120272628</v>
       </c>
       <c r="B10" t="n">
-        <v>90650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624349</v>
+        <v>624550</v>
       </c>
       <c r="R10" t="n">
-        <v>7022391</v>
+        <v>7022411</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,57 +1548,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120272420</v>
+        <v>120272073</v>
       </c>
       <c r="B11" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624396</v>
+        <v>624349</v>
       </c>
       <c r="R11" t="n">
-        <v>7022500</v>
+        <v>7022391</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,50 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120272558</v>
+        <v>120272371</v>
       </c>
       <c r="B12" t="n">
-        <v>90630</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Väster-Pälskamyran, Väster-Pälskamyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624517</v>
+        <v>624367</v>
       </c>
       <c r="R12" t="n">
-        <v>7022444</v>
+        <v>7022541</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1813,12 +1745,7 @@
         <v>120272485</v>
       </c>
       <c r="B13" t="n">
-        <v>90595</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120272004</v>
+        <v>120272566</v>
       </c>
       <c r="B14" t="n">
-        <v>91929</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,13 +1874,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624404</v>
+        <v>624519</v>
       </c>
       <c r="R14" t="n">
-        <v>7022301</v>
+        <v>7022450</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2014,57 +1936,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120273496</v>
+        <v>120272004</v>
       </c>
       <c r="B15" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624803</v>
+        <v>624404</v>
       </c>
       <c r="R15" t="n">
-        <v>7022244</v>
+        <v>7022301</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2120,58 +2033,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120272677</v>
+        <v>120271439</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624576</v>
+        <v>624523</v>
       </c>
       <c r="R16" t="n">
-        <v>7022395</v>
+        <v>7022199</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2230,12 +2133,7 @@
         <v>120271697</v>
       </c>
       <c r="B17" t="n">
-        <v>78296</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,50 +2227,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120273575</v>
+        <v>120272677</v>
       </c>
       <c r="B18" t="n">
-        <v>90918</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624807</v>
+        <v>624576</v>
       </c>
       <c r="R18" t="n">
-        <v>7022241</v>
+        <v>7022395</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2431,15 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120273627</v>
+        <v>120272200</v>
       </c>
       <c r="B19" t="n">
-        <v>90630</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,34 +2340,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624821</v>
+        <v>624385</v>
       </c>
       <c r="R19" t="n">
-        <v>7022235</v>
+        <v>7022487</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2507,6 +2405,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,15 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120273696</v>
+        <v>120273257</v>
       </c>
       <c r="B20" t="n">
-        <v>90630</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,34 +2447,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624864</v>
+        <v>624814</v>
       </c>
       <c r="R20" t="n">
-        <v>7022217</v>
+        <v>7022378</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2609,6 +2512,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,54 +2543,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120273078</v>
+        <v>120272645</v>
       </c>
       <c r="B21" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624816</v>
+        <v>624550</v>
       </c>
       <c r="R21" t="n">
-        <v>7022282</v>
+        <v>7022411</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2741,43 +2645,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120272200</v>
+        <v>120272420</v>
       </c>
       <c r="B22" t="n">
-        <v>57332</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2786,10 +2684,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624385</v>
+        <v>624396</v>
       </c>
       <c r="R22" t="n">
-        <v>7022487</v>
+        <v>7022500</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,11 +2720,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammeltall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2853,55 +2746,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120272645</v>
+        <v>120273078</v>
       </c>
       <c r="B23" t="n">
-        <v>56536</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624550</v>
+        <v>624816</v>
       </c>
       <c r="R23" t="n">
-        <v>7022411</v>
+        <v>7022282</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2960,50 +2847,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120273602</v>
+        <v>120273496</v>
       </c>
       <c r="B24" t="n">
-        <v>90630</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624807</v>
+        <v>624803</v>
       </c>
       <c r="R24" t="n">
-        <v>7022242</v>
+        <v>7022244</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3062,53 +2948,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120271439</v>
+        <v>120273570</v>
       </c>
       <c r="B25" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grundmyran, Grundmyran, Ång</t>
+          <t>Pälskabäcken, Pälskabäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624523</v>
+        <v>624807</v>
       </c>
       <c r="R25" t="n">
-        <v>7022199</v>
+        <v>7022241</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3164,15 +3049,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120273620</v>
+        <v>120272229</v>
       </c>
       <c r="B26" t="n">
-        <v>90918</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3180,34 +3060,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6040186</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pälskabäcken, Pälskabäcken, Ång</t>
+          <t>Grundmyran, Grundmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624821</v>
+        <v>624381</v>
       </c>
       <c r="R26" t="n">
-        <v>7022234</v>
+        <v>7022482</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 40262-2024 artfynd.xlsx
+++ b/artfynd/A 40262-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273575</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272432</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272558</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273602</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273627</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273696</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272628</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272073</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272371</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272485</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272566</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272004</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120271439</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120271697</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272677</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272200</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273257</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,6 +2742,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272645</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2743,6 +2848,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272420</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2844,6 +2954,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273078</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2945,6 +3060,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273496</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3046,6 +3166,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120273570</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3143,8 +3268,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272229</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>